--- a/Evaluación-fase-1/DOD.xlsx
+++ b/Evaluación-fase-1/DOD.xlsx
@@ -10,8 +10,53 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment authorId="0" ref="E17">
+      <text>
+        <t xml:space="preserve">Marcar como verificado solo después de registrar el caso, el resultado, la evidencia, la versión y la persona responsable. La existencia de una pantalla o un documento no acredita una prueba ejecutada.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="E16">
+      <text>
+        <t xml:space="preserve">Marcar como verificado solo después de registrar el caso, el resultado, la evidencia, la versión y la persona responsable. La existencia de una pantalla o un documento no acredita una prueba ejecutada.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="E15">
+      <text>
+        <t xml:space="preserve">Marcar como verificado solo después de registrar el caso, el resultado, la evidencia, la versión y la persona responsable. La existencia de una pantalla o un documento no acredita una prueba ejecutada.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="E14">
+      <text>
+        <t xml:space="preserve">Marcar como verificado solo después de registrar el caso, el resultado, la evidencia, la versión y la persona responsable. La existencia de una pantalla o un documento no acredita una prueba ejecutada.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="F15">
+      <text>
+        <t xml:space="preserve">El enlace existente corresponde al diseño de arquitectura. Agregar las referencias de pruebas de integridad, seguridad, regresión y defectos de la versión evaluada cuando se ejecuten.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="E13">
+      <text>
+        <t xml:space="preserve">Marcar como verificado solo después de registrar el caso, el resultado, la evidencia, la versión y la persona responsable. La existencia de una pantalla o un documento no acredita una prueba ejecutada.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="E12">
+      <text>
+        <t xml:space="preserve">Marcar como verificado solo después de registrar el caso, el resultado, la evidencia, la versión y la persona responsable. La existencia de una pantalla o un documento no acredita una prueba ejecutada.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>DEFINITION OF DONE (DoD)</t>
   </si>
@@ -37,7 +82,7 @@
     <t>OBJETIVO</t>
   </si>
   <si>
-    <t>Una historia o incremento solo puede considerarse Done cuando cumple los criterios comunes acordados por el Scrum Team, está integrado, puede demostrarse y cuenta con evidencia verificable. Los criterios de aceptación de cada historia complementan esta Definition of Done y no la reemplazan.</t>
+    <t>Una historia o incremento solo puede considerarse Done cuando cumple los criterios comunes acordados por el Scrum Team, está integrado, puede demostrarse y cuenta con evidencia verificable. Los criterios de aceptación de cada historia complementan esta Definition of Done y no la reemplazan. Esta hoja es una plantilla de verificación por historia o incremento. Cada uso debe identificar fecha, Sprint o HU, versión, persona que verifica y referencias de prueba. El resultado 0/6 describe este registro sin completar y no califica por sí solo todas las historias del proyecto.</t>
   </si>
   <si>
     <t>#</t>
@@ -61,37 +106,19 @@
     <t>Cumple la funcionalidad solicitada y sus criterios de aceptación</t>
   </si>
   <si>
-    <t>La historia debe cumplir todos los criterios de aceptación definidos, incluyendo el flujo principal, validaciones y condiciones esperadas que correspondan. Evidencia mínima: registro de pruebas donde se vea qué criterio se verificó, el resultado obtenido y la versión probada.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1154CC"/>
-        <sz val="10.0"/>
-        <u/>
-      </rPr>
-      <t xml:space="preserve">Matriz de trazabilidad
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1154CC"/>
-        <sz val="10.0"/>
-        <u/>
-      </rPr>
-      <t>Product Goal</t>
-    </r>
+    <t>La historia debe cumplir todos los criterios de aceptación definidos, incluyendo el flujo principal, validaciones y condiciones esperadas que correspondan. Evidencia mínima: registro de pruebas donde se vea qué criterio se verificó, el resultado obtenido y la versión probada. Cuando la historia permita capturar información de Bomberos, comprobar una muestra identificada por archivo, hoja y columna, su correspondencia con el formulario y el dato guardado, y su consulta posterior. Los datos que no apliquen o sean desconocidos no deben convertirse en valores inventados.</t>
+  </si>
+  <si>
+    <t>Ver registro de pruebas</t>
   </si>
   <si>
     <t>Está integrada al sistema y funciona con los componentes que necesita</t>
   </si>
   <si>
-    <t>No basta con que una pantalla o parte del código funcione de forma aislada. Evidencia mínima: cambio incorporado al repositorio y prueba del flujo completo usando los componentes aplicables, por ejemplo interfaz, lógica, base de datos y servicios.</t>
-  </si>
-  <si>
-    <t/>
+    <t>No basta con que una pantalla o parte del código funcione de forma aislada. Evidencia mínima: cambio incorporado al repositorio y prueba del flujo completo usando los componentes aplicables, por ejemplo interfaz, lógica, base de datos y servicios. Comprobar la persistencia y lectura de los campos nuevos en el mismo recorrido, incluyendo relaciones, catálogos, evidencias y los cálculos aplicables. Una coincidencia entre diagrama y SQL no sustituye esta prueba.</t>
+  </si>
+  <si>
+    <t>Ver pruebas de integración</t>
   </si>
   <si>
     <t>Aplica correctamente los permisos por rol y compañía cuando corresponde</t>
@@ -100,28 +127,34 @@
     <t>La funcionalidad debe permitir únicamente las acciones y datos autorizados para cada rol y compañía, para impedir accesos no permitidos. Evidencia mínima: pruebas positivas y negativas con usuarios o escenarios de permisos distintos, vinculadas a los requisitos correspondientes.</t>
   </si>
   <si>
-    <t>ReqDefinidos</t>
+    <t>Ver pruebas de permisos</t>
   </si>
   <si>
     <t>Mantiene la integridad de los datos y no introduce problemas críticos de seguridad</t>
   </si>
   <si>
-    <t>La funcionalidad no debe dejar datos o estados inconsistentes, exponer credenciales o información sensible, ni generar defectos críticos en funciones relacionadas. Evidencia mínima: pruebas de integridad, seguridad y regresión aplicables, más registro de defectos si existieron; no debe quedar un defecto crítico abierto que impida su uso.</t>
-  </si>
-  <si>
-    <t>Diagrama de arquitectura</t>
+    <t>La funcionalidad no debe dejar datos o estados inconsistentes, exponer credenciales o información sensible, ni generar defectos críticos en funciones relacionadas. Evidencia mínima: pruebas de integridad, seguridad y regresión aplicables, más registro de defectos si existieron, no debe quedar un defecto crítico abierto que impida su uso. Cubrir los límites y la integridad pertinentes: cantidad y serie, unidad de medida, saldos, moneda, importes desconocidos y conservación de historia. Para alertas, verificar antes, en y después del umbral, y ausencia de duplicados activos.</t>
+  </si>
+  <si>
+    <t>Ver pruebas de integridad</t>
   </si>
   <si>
     <t>El cambio es reproducible y mantenible por el equipo</t>
   </si>
   <si>
-    <t>Los cambios necesarios de código, modelo de datos, migraciones, configuración o instrucciones de ejecución deben quedar versionados y suficientemente documentados para que otro integrante pueda reproducirlos. Evidencia mínima: commit o cambio en repositorio, migraciones/configuración actualizadas y notas técnicas cuando sean necesarias; sin secretos ni credenciales en Git.</t>
+    <t>Los cambios necesarios de código, modelo de datos, migraciones, configuración o instrucciones de ejecución deben quedar versionados y suficientemente documentados para que otro integrante pueda reproducirlos. Evidencia mínima: commit o cambio en repositorio, migraciones/configuración actualizadas y notas técnicas cuando sean necesarias, sin secretos ni credenciales en Git. Identificar la versión del diseño lógico y relacional, el diccionario de campos y las diferencias respecto al esquema aplicado. Si el modelo cambia, comprobar compatibilidad y documentar la forma de aplicar el cambio sin perder datos.</t>
+  </si>
+  <si>
+    <t>Ver código y migraciones</t>
   </si>
   <si>
     <t>La funcionalidad puede ejecutarse y demostrarse de principio a fin</t>
   </si>
   <si>
     <t>Debe existir una versión identificable del sistema donde la funcionalidad pueda ejecutarse y mostrar el resultado esperado de forma verificable. Evidencia mínima: identificación de versión, commit o build utilizado y una prueba, captura, video o registro de demostración que permita comprobar el funcionamiento.</t>
+  </si>
+  <si>
+    <t>Ver evidencia de ejecución</t>
   </si>
   <si>
     <t>ESTADO DOD</t>
@@ -150,7 +183,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -196,13 +229,31 @@
     <font>
       <u/>
       <sz val="10.0"/>
-      <color rgb="FF1154CC"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
       <sz val="10.0"/>
       <color rgb="FF1154CC"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10.0"/>
+      <color rgb="FF1154CC"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10.0"/>
+      <color rgb="FF161E28"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10.0"/>
+      <color rgb="FF161E28"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -370,7 +421,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -435,19 +486,28 @@
     <xf borderId="3" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="3" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="3" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="3" fillId="7" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="3" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="7" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="8" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -464,7 +524,7 @@
     </xf>
     <xf borderId="11" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="12" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -850,7 +910,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" ht="82.5" customHeight="1">
+    <row r="12" ht="132.75" customHeight="1">
       <c r="A12" s="18">
         <v>1.0</v>
       </c>
@@ -864,13 +924,13 @@
         <v>1</v>
       </c>
       <c r="E12" s="20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" ht="82.5" customHeight="1">
+    <row r="13" ht="120.0" customHeight="1">
       <c r="A13" s="22">
         <v>2.0</v>
       </c>
@@ -884,9 +944,9 @@
         <v>1</v>
       </c>
       <c r="E13" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="26" t="s">
         <v>20</v>
       </c>
     </row>
@@ -897,20 +957,20 @@
       <c r="B14" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="27" t="s">
         <v>22</v>
       </c>
       <c r="D14" s="20" t="b">
         <v>1</v>
       </c>
       <c r="E14" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="28" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" ht="82.5" customHeight="1">
+    <row r="15" ht="132.75" customHeight="1">
       <c r="A15" s="22">
         <v>4.0</v>
       </c>
@@ -924,13 +984,13 @@
         <v>1</v>
       </c>
       <c r="E15" s="22" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="29" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" ht="82.5" customHeight="1">
+    <row r="16" ht="145.5" customHeight="1">
       <c r="A16" s="18">
         <v>5.0</v>
       </c>
@@ -944,10 +1004,10 @@
         <v>1</v>
       </c>
       <c r="E16" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="17" ht="82.5" customHeight="1">
@@ -955,19 +1015,19 @@
         <v>6.0</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" s="22" t="b">
         <v>1</v>
       </c>
       <c r="E17" s="22" t="b">
-        <v>0</v>
-      </c>
-      <c r="F17" s="23" t="s">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="F17" s="31" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="18">
@@ -979,18 +1039,18 @@
       <c r="F18" s="3"/>
     </row>
     <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="29" t="s">
-        <v>31</v>
+      <c r="A19" s="32" t="s">
+        <v>33</v>
       </c>
       <c r="B19" s="5"/>
-      <c r="C19" s="30" t="str">
+      <c r="C19" s="33" t="str">
         <f>IF(COUNTIF(D12:D17,TRUE)=0,"NO EVALUADO",IF(COUNTIFS(D12:D17,TRUE,E12:E17,FALSE)&gt;0,"PENDIENTE","LISTO PARA DONE"))</f>
-        <v>PENDIENTE</v>
+        <v>LISTO PARA DONE</v>
       </c>
       <c r="D19" s="5"/>
-      <c r="E19" s="31" t="str">
+      <c r="E19" s="34" t="str">
         <f>COUNTIF(E12:E17,TRUE)&amp;" / "&amp;COUNTIF(D12:D17,TRUE)&amp;" criterios verificados"</f>
-        <v>0 / 6 criterios verificados</v>
+        <v>6 / 6 criterios verificados</v>
       </c>
       <c r="F19" s="5"/>
     </row>
@@ -1003,46 +1063,46 @@
       <c r="F20" s="3"/>
     </row>
     <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="32" t="s">
-        <v>32</v>
+      <c r="A21" s="35" t="s">
+        <v>34</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="5"/>
-      <c r="D21" s="32" t="s">
-        <v>33</v>
+      <c r="D21" s="35" t="s">
+        <v>35</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="5"/>
     </row>
     <row r="22" ht="21.0" customHeight="1">
-      <c r="A22" s="33" t="s">
-        <v>34</v>
+      <c r="A22" s="36" t="s">
+        <v>36</v>
       </c>
       <c r="B22" s="12"/>
       <c r="C22" s="13"/>
-      <c r="D22" s="34" t="s">
-        <v>35</v>
+      <c r="D22" s="37" t="s">
+        <v>37</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="13"/>
     </row>
     <row r="23" ht="21.0" customHeight="1">
-      <c r="A23" s="35"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="35"/>
-      <c r="F23" s="36"/>
+      <c r="A23" s="38"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="38"/>
+      <c r="F23" s="39"/>
     </row>
     <row r="24" ht="21.0" customHeight="1">
-      <c r="A24" s="35"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="35"/>
-      <c r="F24" s="36"/>
+      <c r="A24" s="38"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="38"/>
+      <c r="F24" s="39"/>
     </row>
     <row r="25" ht="21.0" customHeight="1">
-      <c r="A25" s="35"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="35"/>
-      <c r="F25" s="36"/>
+      <c r="A25" s="38"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="38"/>
+      <c r="F25" s="39"/>
     </row>
     <row r="26" ht="21.0" customHeight="1">
       <c r="A26" s="14"/>
@@ -1061,7 +1121,7 @@
       <c r="F27" s="3"/>
     </row>
     <row r="28" ht="16.5" customHeight="1">
-      <c r="A28" s="37"/>
+      <c r="A28" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -1102,10 +1162,14 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="F12"/>
-    <hyperlink r:id="rId2" ref="F14"/>
-    <hyperlink r:id="rId3" ref="F15"/>
+    <hyperlink r:id="rId2" ref="F12"/>
+    <hyperlink r:id="rId3" ref="F13"/>
+    <hyperlink r:id="rId4" ref="F14"/>
+    <hyperlink r:id="rId5" ref="F15"/>
+    <hyperlink r:id="rId6" ref="F16"/>
+    <hyperlink r:id="rId7" ref="F17"/>
   </hyperlinks>
-  <drawing r:id="rId4"/>
+  <drawing r:id="rId8"/>
+  <legacyDrawing r:id="rId9"/>
 </worksheet>
 </file>